--- a/ART760/ART760_template.xlsx
+++ b/ART760/ART760_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/jamarin_upv_edu_es/Documents/R/ART-760/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_C24B2A7B8AF861F5B43C2FC053809FC177709ED8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F414110-0338-409F-AC0D-07C47AA0AA13}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_C24B2A7B8AF861F5B43C2FC053809FC177709ED8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CE003A-FBA3-4AE4-955F-90BF9E0B4FFD}"/>
   <bookViews>
-    <workbookView xWindow="29085" yWindow="-7230" windowWidth="15915" windowHeight="15195" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29085" yWindow="-10740" windowWidth="15915" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
